--- a/100040000/raw_data.xlsx
+++ b/100040000/raw_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carcheme\PycharmProjects\gyan\mini_project\100040000\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carla\clariant\mini_project\100040000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B1FD27-B7A8-4266-9A1F-0FEE3D09591B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9534B53B-CD9C-4FE8-8C3C-331C6470FF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1830" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{83AC14B2-2E1F-4BB3-8D35-B9BFFD3D8107}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{83AC14B2-2E1F-4BB3-8D35-B9BFFD3D8107}"/>
   </bookViews>
   <sheets>
     <sheet name="2-122941" sheetId="6" r:id="rId1"/>

--- a/100040000/raw_data.xlsx
+++ b/100040000/raw_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carla\clariant\mini_project\100040000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9534B53B-CD9C-4FE8-8C3C-331C6470FF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C27762-9C47-4D11-A9B2-42B724827807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{83AC14B2-2E1F-4BB3-8D35-B9BFFD3D8107}"/>
   </bookViews>
@@ -3364,16 +3364,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
+      <xdr:rowOff>52387</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>

--- a/100040000/raw_data.xlsx
+++ b/100040000/raw_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carla\clariant\mini_project\100040000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C27762-9C47-4D11-A9B2-42B724827807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2444FAA0-0A22-4197-951A-C79508A939AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{83AC14B2-2E1F-4BB3-8D35-B9BFFD3D8107}"/>
   </bookViews>

--- a/100040000/raw_data.xlsx
+++ b/100040000/raw_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carla\clariant\mini_project\100040000\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carcheme\PycharmProjects\gyan\mini_project\100040000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2444FAA0-0A22-4197-951A-C79508A939AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F067EA4-E8EE-46AE-A04B-D9CB8E2E19D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{83AC14B2-2E1F-4BB3-8D35-B9BFFD3D8107}"/>
+    <workbookView xWindow="28680" yWindow="-1830" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{83AC14B2-2E1F-4BB3-8D35-B9BFFD3D8107}"/>
   </bookViews>
   <sheets>
     <sheet name="2-122941" sheetId="6" r:id="rId1"/>
@@ -1610,6 +1610,380 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="6350" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525">
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:errBars>
+            <c:errDir val="y"/>
+            <c:errBarType val="minus"/>
+            <c:errValType val="percentage"/>
+            <c:noEndCap val="1"/>
+            <c:val val="100"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="241300" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'2-122943'!$J$2:$J$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'2-122943'!$K$2:$K$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5C7C-47BB-B4ED-FABBF895A966}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1446871344"/>
+        <c:axId val="1446872784"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1446871344"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1446872784"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1446872784"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1446871344"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1730,6 +2104,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2763,6 +3177,522 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3364,16 +4294,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3393,6 +4323,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>261937</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>566737</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6956C2EE-7814-EB48-7509-99A6F4657D1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>

--- a/100040000/raw_data.xlsx
+++ b/100040000/raw_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carcheme\PycharmProjects\gyan\mini_project\100040000\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carla\clariant\mini_project\100040000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F067EA4-E8EE-46AE-A04B-D9CB8E2E19D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4566407-094A-494F-8B79-2EF56B9672DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1830" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{83AC14B2-2E1F-4BB3-8D35-B9BFFD3D8107}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{83AC14B2-2E1F-4BB3-8D35-B9BFFD3D8107}"/>
   </bookViews>
   <sheets>
     <sheet name="2-122941" sheetId="6" r:id="rId1"/>
@@ -85,12 +85,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -125,12 +131,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1452,7 +1459,7 @@
         <c:crossAx val="838029408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="2"/>
+        <c:majorUnit val="1"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="838029408"/>
@@ -4664,6 +4671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E184353-1CFB-446A-A81A-D18C23793B52}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6430,6 +6438,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{500452F6-1F54-4F14-A3A1-965B9FE55121}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:L200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8220,6 +8229,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A7B6B71-1464-4720-A6A3-1B702730BA59}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:K200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8335,7 +8345,7 @@
       <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>3.1859999999999999</v>
       </c>
       <c r="H5">
@@ -8355,7 +8365,7 @@
       <c r="A6">
         <v>6</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>3.3239999999999998</v>
       </c>
       <c r="H6">
@@ -8594,7 +8604,7 @@
       <c r="A23">
         <v>23</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="3">
         <v>2.2469999999999999</v>
       </c>
     </row>
@@ -8826,7 +8836,7 @@
       <c r="A52">
         <v>52</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="3">
         <v>3.5089999999999999</v>
       </c>
     </row>
@@ -8914,7 +8924,7 @@
       <c r="A63">
         <v>63</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="3">
         <v>2.2389999999999999</v>
       </c>
     </row>
@@ -8922,7 +8932,7 @@
       <c r="A64">
         <v>64</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="3">
         <v>2.819</v>
       </c>
     </row>
@@ -8946,7 +8956,7 @@
       <c r="A67">
         <v>67</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="3">
         <v>2.7970000000000002</v>
       </c>
     </row>
@@ -8954,7 +8964,7 @@
       <c r="A68">
         <v>68</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="3">
         <v>3.7170000000000001</v>
       </c>
     </row>
@@ -9106,7 +9116,7 @@
       <c r="A87">
         <v>87</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="3">
         <v>2.819</v>
       </c>
     </row>
@@ -9202,7 +9212,7 @@
       <c r="A99">
         <v>99</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="3">
         <v>3.8279999999999998</v>
       </c>
     </row>
@@ -9346,7 +9356,7 @@
       <c r="A117">
         <v>117</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="3">
         <v>3.9460000000000002</v>
       </c>
     </row>
@@ -9410,7 +9420,7 @@
       <c r="A125">
         <v>125</v>
       </c>
-      <c r="B125">
+      <c r="B125" s="3">
         <v>3.8279999999999998</v>
       </c>
     </row>
@@ -9822,7 +9832,7 @@
         <v>10.49</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>177</v>
       </c>
@@ -9830,7 +9840,7 @@
         <v>11.831</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>178</v>
       </c>
@@ -9838,7 +9848,7 @@
         <v>8.3989999999999991</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>179</v>
       </c>
@@ -9846,7 +9856,7 @@
         <v>8.1630000000000003</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>180</v>
       </c>
@@ -9854,7 +9864,7 @@
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>181</v>
       </c>
@@ -9862,7 +9872,7 @@
         <v>7.0019999999999998</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>182</v>
       </c>
@@ -9870,7 +9880,7 @@
         <v>6.7169999999999996</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>183</v>
       </c>
@@ -9878,7 +9888,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>184</v>
       </c>
@@ -9886,7 +9896,7 @@
         <v>4.8570000000000002</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>185</v>
       </c>
@@ -9894,7 +9904,7 @@
         <v>8.0500000000000007</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>186</v>
       </c>
@@ -9902,7 +9912,7 @@
         <v>8.7479999999999993</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>187</v>
       </c>
@@ -9910,15 +9920,18 @@
         <v>8.6359999999999992</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>188</v>
       </c>
       <c r="B188">
         <v>5.4619999999999997</v>
       </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E188">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>189</v>
       </c>
@@ -9926,7 +9939,7 @@
         <v>8.2520000000000007</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>190</v>
       </c>
@@ -9934,7 +9947,7 @@
         <v>7.2080000000000002</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>191</v>
       </c>
@@ -9942,7 +9955,7 @@
         <v>11.106999999999999</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>192</v>
       </c>
